--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484315_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484315_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1915</v>
+        <v>-0.491</v>
       </c>
       <c r="E3" t="n">
         <v>1.5306</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7221</v>
+        <v>-2.0217</v>
       </c>
       <c r="G3" t="n">
         <v>0.2019</v>
@@ -688,13 +688,13 @@
         <v>0.7814</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3312</v>
+        <v>0.0316</v>
       </c>
       <c r="T3" t="n">
         <v>-0.4015</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7327</v>
+        <v>0.4332</v>
       </c>
       <c r="V3" t="n">
         <v>0.6428</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.7216</v>
+        <v>-1.85</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3441</v>
+        <v>0.243</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0657</v>
+        <v>-2.093</v>
       </c>
       <c r="G4" t="n">
         <v>0.009299999999999999</v>
@@ -766,13 +766,13 @@
         <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2686</v>
+        <v>-0.3969</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.22</v>
+        <v>-0.3211</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0486</v>
+        <v>-0.0759</v>
       </c>
       <c r="V4" t="n">
         <v>-1.4624</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.9216</v>
+        <v>-1.8592</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7518</v>
+        <v>-1.09</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1697</v>
+        <v>-0.7692</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.16</v>
+        <v>-2.8525</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0809</v>
+        <v>0.1696</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0792</v>
+        <v>-3.0221</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.3495</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1177</v>
+        <v>1.6168</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6741</v>
+        <v>-1.2673</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3682</v>
+        <v>-3.202</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.4472</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4051</v>
+        <v>-1.7548</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4691</v>
+        <v>0.1822</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9701</v>
+        <v>-0.2674</v>
       </c>
       <c r="U5" t="n">
-        <v>0.499</v>
+        <v>0.4496</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2772</v>
+        <v>0.4204</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2772</v>
+        <v>0.4204</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3496</v>
+        <v>-2.1751</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7166</v>
+        <v>-1.98</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.633</v>
+        <v>-0.1951</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.8525</v>
+        <v>-1.8199</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1696</v>
+        <v>0.0555</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.0221</v>
+        <v>-1.8754</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3495</v>
+        <v>0.3681</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6168</v>
+        <v>1.0284</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2673</v>
+        <v>-0.6603</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.202</v>
+        <v>-2.188</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4472</v>
+        <v>-0.9729</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7548</v>
+        <v>-1.2152</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R6" t="n">
         <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3083</v>
+        <v>0.4746</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8941</v>
+        <v>-0.1993</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5858</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4204</v>
+        <v>-0.2437</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4204</v>
+        <v>-0.2437</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6618</v>
+        <v>-3.2545</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3033</v>
+        <v>-1.3966</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3585</v>
+        <v>-1.8578</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8199</v>
+        <v>-2.152</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0555</v>
+        <v>0.8703</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8754</v>
+        <v>-3.0223</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3681</v>
+        <v>1.25</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0284</v>
+        <v>1.8432</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6603</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.188</v>
+        <v>-3.402</v>
       </c>
       <c r="N7" t="n">
         <v>-0.9729</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2152</v>
+        <v>-2.4291</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0121</v>
+        <v>-0.7333</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5226</v>
+        <v>-0.6849</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5105</v>
+        <v>-0.0483</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2437</v>
+        <v>1.5842</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2437</v>
+        <v>0.4204</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2974</v>
+        <v>-3.4456</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9221</v>
+        <v>-3.2486</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3753</v>
+        <v>-0.197</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.152</v>
+        <v>-2.16</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8703</v>
+        <v>-1.0809</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.0223</v>
+        <v>-1.0792</v>
       </c>
       <c r="J8" t="n">
-        <v>1.25</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8432</v>
+        <v>-0.1177</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6741</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.402</v>
+        <v>-1.3682</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9729</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.4291</v>
+        <v>-0.4051</v>
       </c>
       <c r="P8" t="n">
         <v>-1.9534</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1255</v>
+        <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7762</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2105</v>
+        <v>0.4733</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5658</v>
+        <v>0.4718</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5842</v>
+        <v>-0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4204</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.7657</v>
+        <v>-4.6136</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6496</v>
+        <v>-3.2252</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1161</v>
+        <v>-1.3884</v>
       </c>
       <c r="G9" t="n">
         <v>-5.459</v>
@@ -1156,13 +1156,13 @@
         <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>0.498</v>
+        <v>0.65</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2805</v>
+        <v>0.1439</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7784</v>
+        <v>0.5061</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.8023</v>
+        <v>-5.4172</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0286</v>
+        <v>-2.7252</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7737</v>
+        <v>-2.692</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5594</v>
@@ -1234,13 +1234,13 @@
         <v>0.3907</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0708</v>
+        <v>-0.6858</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4842</v>
+        <v>-0.1808</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5867</v>
+        <v>-0.5049</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6093</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-23.7115</v>
+        <v>-23.1062</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.5578</v>
+        <v>-11.9525</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.1536</v>
+        <v>-11.1537</v>
       </c>
       <c r="G11" t="n">
         <v>-16.7916</v>
@@ -1285,7 +1285,7 @@
         <v>-19.5607</v>
       </c>
       <c r="J11" t="n">
-        <v>2.291300000000001</v>
+        <v>2.2913</v>
       </c>
       <c r="K11" t="n">
         <v>9.7044</v>
@@ -1312,16 +1312,16 @@
         <v>8.7905</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1377000000000002</v>
+        <v>0.4675</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.1038</v>
+        <v>-1.4983</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9658</v>
+        <v>1.966</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0548000000000004</v>
+        <v>0.05480000000000018</v>
       </c>
       <c r="W11" t="n">
         <v>2.882</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9097</v>
+        <v>4.2848</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7552</v>
+        <v>3.0676</v>
       </c>
       <c r="F12" t="n">
-        <v>4.1545</v>
+        <v>1.2172</v>
       </c>
       <c r="G12" t="n">
-        <v>2.0899</v>
+        <v>3.0631</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2267</v>
+        <v>0.5538</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8632</v>
+        <v>2.5093</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8498</v>
+        <v>3.2973</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6603</v>
+        <v>1.8662</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1895</v>
+        <v>1.4311</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2401</v>
+        <v>-0.2342</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4336</v>
+        <v>-1.3123</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6737</v>
+        <v>1.0782</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7348</v>
+        <v>2.1488</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4839</v>
+        <v>0.659</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3044</v>
+        <v>0.1377</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1796</v>
+        <v>0.5212</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5545</v>
+        <v>-0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5545</v>
+        <v>0.6093</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3407</v>
+        <v>4.1672</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0676</v>
+        <v>0.3396</v>
       </c>
       <c r="F13" t="n">
-        <v>1.273</v>
+        <v>3.8277</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0631</v>
+        <v>2.0899</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5538</v>
+        <v>1.2267</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5093</v>
+        <v>0.8632</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2973</v>
+        <v>1.8498</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8662</v>
+        <v>1.6603</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4311</v>
+        <v>0.1895</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2342</v>
+        <v>0.2401</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3123</v>
+        <v>-0.4336</v>
       </c>
       <c r="O13" t="n">
-        <v>1.0782</v>
+        <v>0.6737</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1488</v>
+        <v>2.7348</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7148</v>
+        <v>0.7415</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1377</v>
+        <v>-0.1112</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.8527</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6093</v>
+        <v>0.5545</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6093</v>
+        <v>0.5545</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.273</v>
+        <v>4.0235</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1019</v>
+        <v>4.3981</v>
       </c>
       <c r="F14" t="n">
-        <v>0.171</v>
+        <v>-0.3746</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4282</v>
+        <v>2.7331</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2154</v>
+        <v>-1.5567</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2128</v>
+        <v>4.2898</v>
       </c>
       <c r="J14" t="n">
-        <v>2.927</v>
+        <v>4.3155</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6577</v>
+        <v>0.4298</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2692</v>
+        <v>3.8857</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4988</v>
+        <v>-1.5824</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4423</v>
+        <v>-1.9864</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9435</v>
+        <v>0.4041</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7779</v>
+        <v>0.1183</v>
       </c>
       <c r="T14" t="n">
-        <v>1.175</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6029</v>
+        <v>0.0357</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.24</v>
+        <v>3.6929</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1835</v>
+        <v>2.1781</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0565</v>
+        <v>1.5147</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0425</v>
+        <v>1.8931</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5068</v>
+        <v>-1.925</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5357</v>
+        <v>3.8182</v>
       </c>
       <c r="J15" t="n">
-        <v>3.002</v>
+        <v>3.2903</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0054</v>
+        <v>0.1458</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9966</v>
+        <v>3.1445</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0405</v>
+        <v>-1.3971</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4986</v>
+        <v>-2.0708</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5391</v>
+        <v>0.6737</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5756</v>
+        <v>-0.4505</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0289</v>
+        <v>-0.7447</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4533</v>
+        <v>0.2943</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1638</v>
+        <v>1.2735</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1638</v>
+        <v>0.6093</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9163</v>
+        <v>3.4471</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5892</v>
+        <v>3.4953</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.0482</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7331</v>
+        <v>2.4282</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5567</v>
+        <v>0.2154</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2898</v>
+        <v>2.2128</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3155</v>
+        <v>2.927</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4298</v>
+        <v>1.6577</v>
       </c>
       <c r="L16" t="n">
-        <v>3.8857</v>
+        <v>1.2692</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5824</v>
+        <v>-0.4988</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9864</v>
+        <v>-1.4423</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4041</v>
+        <v>0.9435</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9888</v>
+        <v>0.952</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.5683</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2625</v>
+        <v>0.3837</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6582</v>
+        <v>3.3878</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4703</v>
+        <v>1.3857</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1879</v>
+        <v>2.0021</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8931</v>
+        <v>3.0425</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.925</v>
+        <v>0.5068</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8182</v>
+        <v>2.5357</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2903</v>
+        <v>3.002</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1458</v>
+        <v>1.0054</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1445</v>
+        <v>1.9966</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3971</v>
+        <v>0.0405</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0708</v>
+        <v>-0.4986</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6737</v>
+        <v>0.5391</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4851</v>
+        <v>-0.4278</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4525</v>
+        <v>-0.8267</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0326</v>
+        <v>0.3988</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2735</v>
+        <v>1.1638</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6093</v>
+        <v>1.1638</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9908</v>
+        <v>1.9312</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6887</v>
+        <v>1.3854</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3021</v>
+        <v>0.5458</v>
       </c>
       <c r="G18" t="n">
         <v>0.531</v>
@@ -1858,13 +1858,13 @@
         <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3231</v>
+        <v>0.2635</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6219</v>
+        <v>0.3186</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2989</v>
+        <v>-0.0551</v>
       </c>
       <c r="V18" t="n">
         <v>0.9414</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1601</v>
+        <v>0.4415</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1867</v>
+        <v>-1.8834</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0266</v>
+        <v>2.3248</v>
       </c>
       <c r="G19" t="n">
         <v>0.8033</v>
@@ -1936,13 +1936,13 @@
         <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2722</v>
+        <v>-0.6707</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0289</v>
+        <v>-0.7255</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2433</v>
+        <v>0.0549</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2772</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4571</v>
+        <v>-0.9903</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5161</v>
+        <v>-3.2128</v>
       </c>
       <c r="F20" t="n">
-        <v>2.059</v>
+        <v>2.2224</v>
       </c>
       <c r="G20" t="n">
         <v>0.2073</v>
@@ -2014,13 +2014,13 @@
         <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8401999999999999</v>
+        <v>-0.3735</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9684</v>
+        <v>-0.665</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1281</v>
+        <v>0.2916</v>
       </c>
       <c r="V20" t="n">
         <v>-1.6056</v>
@@ -2047,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>23.7115</v>
+        <v>24.3857</v>
       </c>
       <c r="E21" t="n">
         <v>11.1536</v>
       </c>
       <c r="F21" t="n">
-        <v>12.5577</v>
+        <v>13.2319</v>
       </c>
       <c r="G21" t="n">
         <v>16.7915</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.769200000000001</v>
+        <v>-2.7692</v>
       </c>
       <c r="I21" t="n">
         <v>19.5608</v>
@@ -2068,7 +2068,7 @@
         <v>19.083</v>
       </c>
       <c r="K21" t="n">
-        <v>6.935300000000001</v>
+        <v>6.9353</v>
       </c>
       <c r="L21" t="n">
         <v>12.1476</v>
@@ -2086,22 +2086,22 @@
         <v>6.837</v>
       </c>
       <c r="Q21" t="n">
-        <v>-8.790299999999998</v>
+        <v>-8.7903</v>
       </c>
       <c r="R21" t="n">
         <v>15.6274</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1377999999999998</v>
+        <v>0.8118000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.966</v>
+        <v>-1.9659</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1037</v>
+        <v>2.7778</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.05479999999999996</v>
+        <v>-0.05479999999999974</v>
       </c>
       <c r="W21" t="n">
         <v>2.8272</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484315_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484315_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Y. BOULHROUZI MADANI</t>
+          <t>M. PACÍFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,28 +570,28 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0605</v>
+        <v>0.614</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0605</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -613,10 +618,10 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0605</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0605</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -626,12 +631,17 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>Y. BOULHROUZI MADANI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.491</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5306</v>
+        <v>-0.0605</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0217</v>
+        <v>0.0605</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2019</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3.088</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.8861</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1944</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.056</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8616</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9925</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.968</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0245</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0316</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4015</v>
+        <v>-0.0605</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4332</v>
+        <v>0.0605</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6428</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2437</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.85</v>
+        <v>-0.491</v>
       </c>
       <c r="E4" t="n">
-        <v>0.243</v>
+        <v>1.5306</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.093</v>
+        <v>-2.0217</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.2019</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7503</v>
+        <v>3.088</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.741</v>
+        <v>-2.8861</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1231</v>
+        <v>3.1944</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1092</v>
+        <v>4.056</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0138</v>
+        <v>-0.8616</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1137</v>
+        <v>-2.9925</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3589</v>
+        <v>-0.968</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7548</v>
+        <v>-2.0245</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3969</v>
+        <v>0.0316</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3211</v>
+        <v>-0.4015</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0759</v>
+        <v>0.4332</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.4624</v>
+        <v>0.6428</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3869</v>
+        <v>0.8865</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0754</v>
+        <v>-0.2437</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>F. GASPAR AGUILAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.8592</v>
+        <v>-1.85</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.09</v>
+        <v>0.243</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7692</v>
+        <v>-2.093</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.8525</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1696</v>
+        <v>1.7503</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.0221</v>
+        <v>-1.741</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3495</v>
+        <v>2.1231</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6168</v>
+        <v>2.1092</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2673</v>
+        <v>0.0138</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.202</v>
+        <v>-2.1137</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4472</v>
+        <v>-0.3589</v>
       </c>
       <c r="O5" t="n">
         <v>-1.7548</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1822</v>
+        <v>-0.3969</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2674</v>
+        <v>-0.3211</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4496</v>
+        <v>-0.0759</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4204</v>
+        <v>-1.4624</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4204</v>
+        <v>-1.0754</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1751</v>
+        <v>-1.8592</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.98</v>
+        <v>-1.09</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1951</v>
+        <v>-0.7692</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8199</v>
+        <v>-2.8525</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0555</v>
+        <v>0.1696</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8754</v>
+        <v>-3.0221</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3681</v>
+        <v>0.3495</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0284</v>
+        <v>1.6168</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6603</v>
+        <v>-1.2673</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.188</v>
+        <v>-3.202</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9729</v>
+        <v>-1.4472</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2152</v>
+        <v>-1.7548</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R6" t="n">
         <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4746</v>
+        <v>0.1822</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1993</v>
+        <v>-0.2674</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.4496</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2437</v>
+        <v>0.4204</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2437</v>
+        <v>0.4204</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.2545</v>
+        <v>-2.1751</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3966</v>
+        <v>-1.98</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8578</v>
+        <v>-0.1951</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.152</v>
+        <v>-1.8199</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8703</v>
+        <v>0.0555</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0223</v>
+        <v>-1.8754</v>
       </c>
       <c r="J7" t="n">
-        <v>1.25</v>
+        <v>0.3681</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8432</v>
+        <v>1.0284</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6603</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.402</v>
+        <v>-2.188</v>
       </c>
       <c r="N7" t="n">
         <v>-0.9729</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.4291</v>
+        <v>-1.2152</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9534</v>
+        <v>-0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1255</v>
+        <v>-2.1488</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7333</v>
+        <v>0.4746</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6849</v>
+        <v>-0.1993</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0483</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5842</v>
+        <v>-0.2437</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4204</v>
+        <v>-0.2437</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4456</v>
+        <v>-3.2545</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2486</v>
+        <v>-1.3966</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.197</v>
+        <v>-1.8578</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.16</v>
+        <v>-2.152</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0809</v>
+        <v>0.8703</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0792</v>
+        <v>-3.0223</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7917999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1177</v>
+        <v>1.8432</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6741</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3682</v>
+        <v>-3.402</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.9729</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4051</v>
+        <v>-2.4291</v>
       </c>
       <c r="P8" t="n">
         <v>-1.9534</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-3.1255</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9451000000000001</v>
+        <v>-0.7333</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4733</v>
+        <v>-0.6849</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4718</v>
+        <v>-0.0483</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>1.5842</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0.4204</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6136</v>
+        <v>-3.4456</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2252</v>
+        <v>-3.2486</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3884</v>
+        <v>-0.197</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.459</v>
+        <v>-2.16</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8176</v>
+        <v>-1.0809</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.6413</v>
+        <v>-1.0792</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.611</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9146</v>
+        <v>-0.1177</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.6964</v>
+        <v>-0.6741</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.848</v>
+        <v>-1.3682</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.903</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9449</v>
+        <v>-0.4051</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>0.65</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1439</v>
+        <v>0.4733</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5061</v>
+        <v>0.4718</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4172</v>
+        <v>-4.6136</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7252</v>
+        <v>-3.2252</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.692</v>
+        <v>-1.3884</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5594</v>
+        <v>-5.459</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2661</v>
+        <v>-1.8176</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2933</v>
+        <v>-3.6413</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.591</v>
+        <v>-3.611</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08309999999999999</v>
+        <v>-0.9146</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6741</v>
+        <v>-2.6964</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9684</v>
+        <v>-1.848</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3492</v>
+        <v>-0.903</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6192</v>
+        <v>-0.9449</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6858</v>
+        <v>0.65</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1808</v>
+        <v>0.1439</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5049</v>
+        <v>0.5061</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,151 +1317,157 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-23.1062</v>
+        <v>-6.0312</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.9525</v>
+        <v>-3.3392</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.1537</v>
+        <v>-2.692</v>
       </c>
       <c r="G11" t="n">
-        <v>-16.7916</v>
+        <v>-3.1733</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7691</v>
+        <v>-0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-19.5607</v>
+        <v>-2.2933</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2913</v>
+        <v>-1.2049</v>
       </c>
       <c r="K11" t="n">
-        <v>9.7044</v>
+        <v>-0.5308</v>
       </c>
       <c r="L11" t="n">
-        <v>-7.413200000000001</v>
+        <v>-0.6741</v>
       </c>
       <c r="M11" t="n">
-        <v>-19.0828</v>
+        <v>-1.9684</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.9353</v>
+        <v>-0.3492</v>
       </c>
       <c r="O11" t="n">
-        <v>-12.1476</v>
+        <v>-1.6192</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.8369</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-15.6275</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>8.7905</v>
+        <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4675</v>
+        <v>-0.6858</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4983</v>
+        <v>-0.1808</v>
       </c>
       <c r="U11" t="n">
-        <v>1.966</v>
+        <v>-0.5049</v>
       </c>
       <c r="V11" t="n">
-        <v>0.05480000000000018</v>
+        <v>-0.6093</v>
       </c>
       <c r="W11" t="n">
-        <v>2.882</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8271</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>C.B. CUARTE DE HUERVA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2848</v>
+        <v>-23.1062</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0676</v>
+        <v>-11.9525</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2172</v>
+        <v>-11.1537</v>
       </c>
       <c r="G12" t="n">
-        <v>3.0631</v>
+        <v>-16.7915</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5538</v>
+        <v>2.7692</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5093</v>
+        <v>-19.5607</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2973</v>
+        <v>2.2914</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8662</v>
+        <v>9.704500000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4311</v>
+        <v>-7.413200000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2342</v>
+        <v>-19.0828</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3123</v>
+        <v>-6.9353</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0782</v>
+        <v>-12.1476</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1721</v>
+        <v>-6.8369</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-15.6275</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1488</v>
+        <v>8.790500000000002</v>
       </c>
       <c r="S12" t="n">
-        <v>0.659</v>
+        <v>0.4675000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1377</v>
+        <v>-1.4983</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5212</v>
+        <v>1.966</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6093</v>
+        <v>0.05480000000000018</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6093</v>
+        <v>2.882</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2186</v>
-      </c>
+        <v>-2.8271</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1672</v>
+        <v>4.2848</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3396</v>
+        <v>3.0676</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8277</v>
+        <v>1.2172</v>
       </c>
       <c r="G13" t="n">
-        <v>2.0899</v>
+        <v>3.0631</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2267</v>
+        <v>0.5538</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8632</v>
+        <v>2.5093</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8498</v>
+        <v>3.2973</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6603</v>
+        <v>1.8662</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1895</v>
+        <v>1.4311</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2401</v>
+        <v>-0.2342</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4336</v>
+        <v>-1.3123</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6737</v>
+        <v>1.0782</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7348</v>
+        <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7415</v>
+        <v>0.659</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1112</v>
+        <v>0.1377</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8527</v>
+        <v>0.5212</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5545</v>
+        <v>-0.6093</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5545</v>
+        <v>0.6093</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0235</v>
+        <v>4.1672</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3981</v>
+        <v>0.3396</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3746</v>
+        <v>3.8277</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7331</v>
+        <v>2.0899</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5567</v>
+        <v>1.2267</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2898</v>
+        <v>0.8632</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3155</v>
+        <v>1.8498</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4298</v>
+        <v>1.6603</v>
       </c>
       <c r="L14" t="n">
-        <v>3.8857</v>
+        <v>0.1895</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5824</v>
+        <v>0.2401</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9864</v>
+        <v>-0.4336</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4041</v>
+        <v>0.6737</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1721</v>
+        <v>2.7348</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1183</v>
+        <v>0.7415</v>
       </c>
       <c r="T14" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.1112</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0357</v>
+        <v>0.8527</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6929</v>
+        <v>3.7165</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1781</v>
+        <v>4.0911</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5147</v>
+        <v>-0.3746</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8931</v>
+        <v>2.4261</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.925</v>
+        <v>-1.8637</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8182</v>
+        <v>4.2898</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2903</v>
+        <v>4.0085</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1458</v>
+        <v>0.1228</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1445</v>
+        <v>3.8857</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3971</v>
+        <v>-1.5824</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.0708</v>
+        <v>-1.9864</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6737</v>
+        <v>0.4041</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4505</v>
+        <v>0.1183</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7447</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2943</v>
+        <v>0.0357</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2735</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4471</v>
+        <v>3.6559</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4953</v>
+        <v>3.6559</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0482</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4282</v>
+        <v>3.6559</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2154</v>
+        <v>1.2279</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2128</v>
+        <v>2.4279</v>
       </c>
       <c r="J16" t="n">
-        <v>2.927</v>
+        <v>3.6559</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6577</v>
+        <v>1.2279</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2692</v>
+        <v>2.4279</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4988</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4423</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.952</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5683</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3837</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3878</v>
+        <v>3.4471</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3857</v>
+        <v>3.4953</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0021</v>
+        <v>-0.0482</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0425</v>
+        <v>2.4282</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5068</v>
+        <v>0.2154</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5357</v>
+        <v>2.2128</v>
       </c>
       <c r="J17" t="n">
-        <v>3.002</v>
+        <v>2.927</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0054</v>
+        <v>1.6577</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9966</v>
+        <v>1.2692</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0405</v>
+        <v>-0.4988</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4986</v>
+        <v>-1.4423</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5391</v>
+        <v>0.9435</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4278</v>
+        <v>0.952</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8267</v>
+        <v>0.5683</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3988</v>
+        <v>0.3837</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1638</v>
+        <v>-1.4959</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9312</v>
+        <v>3.3878</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3854</v>
+        <v>1.3857</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5458</v>
+        <v>2.0021</v>
       </c>
       <c r="G18" t="n">
-        <v>0.531</v>
+        <v>3.0425</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3303</v>
+        <v>0.5068</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8612</v>
+        <v>2.5357</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8249</v>
+        <v>3.002</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0422</v>
+        <v>1.0054</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7827</v>
+        <v>1.9966</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2939</v>
+        <v>0.0405</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3725</v>
+        <v>-0.4986</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0786</v>
+        <v>0.5391</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2635</v>
+        <v>-0.4278</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3186</v>
+        <v>-0.8267</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0551</v>
+        <v>0.3988</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>1.1638</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>1.1638</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4415</v>
+        <v>1.214</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8834</v>
+        <v>1.214</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3248</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8033</v>
+        <v>1.214</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4515</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2548</v>
+        <v>1.214</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1811</v>
+        <v>1.214</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2226</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0415</v>
+        <v>1.214</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9844000000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2289</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2134</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6707</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7255</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9903</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2128</v>
+        <v>0.1714</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2224</v>
+        <v>0.5458</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2073</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-1.3303</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2158</v>
+        <v>0.6473</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2427</v>
+        <v>-0.3891</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3505</v>
+        <v>0.0422</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.4313</v>
       </c>
       <c r="M20" t="n">
-        <v>0.45</v>
+        <v>-0.2939</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3589</v>
+        <v>-1.3725</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8089</v>
+        <v>1.0786</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3735</v>
+        <v>0.2635</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.665</v>
+        <v>0.3186</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2916</v>
+        <v>-0.0551</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.6056</v>
+        <v>0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.3283</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,68 +2143,401 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.8834</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.3248</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8033</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.4515</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2548</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.1811</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.2226</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.9844000000000001</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.2289</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.2134</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.6707</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.7255</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A. MARTÍN ADELANTADO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A. VINALLONGA GOMEZ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.4777</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.5147</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.7627</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-3.153</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.3902</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.3656</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.0821</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.7165</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.3971</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-2.0708</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.6737</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.4505</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.7447</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.2735</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>M. SALMERON SEGU</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.9903</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.2128</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.2224</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.2073</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2158</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.2427</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.5931999999999999</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.3589</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8089</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.3735</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.665</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.6056</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-1.3283</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484315_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>24.3857</v>
       </c>
-      <c r="E21" t="n">
-        <v>11.1536</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="E25" t="n">
+        <v>11.1537</v>
+      </c>
+      <c r="F25" t="n">
         <v>13.2319</v>
       </c>
-      <c r="G21" t="n">
-        <v>16.7915</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-2.7692</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="G25" t="n">
+        <v>16.7916</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.7693</v>
+      </c>
+      <c r="I25" t="n">
         <v>19.5608</v>
       </c>
-      <c r="J21" t="n">
-        <v>19.083</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="J25" t="n">
+        <v>19.08299999999999</v>
+      </c>
+      <c r="K25" t="n">
         <v>6.9353</v>
       </c>
-      <c r="L21" t="n">
-        <v>12.1476</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-2.291399999999999</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-9.7043</v>
-      </c>
-      <c r="O21" t="n">
+      <c r="L25" t="n">
+        <v>12.1475</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.2914</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-9.704300000000002</v>
+      </c>
+      <c r="O25" t="n">
         <v>7.4132</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P25" t="n">
         <v>6.837</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q25" t="n">
         <v>-8.7903</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R25" t="n">
         <v>15.6274</v>
       </c>
-      <c r="S21" t="n">
-        <v>0.8118000000000001</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="S25" t="n">
+        <v>0.8118000000000003</v>
+      </c>
+      <c r="T25" t="n">
         <v>-1.9659</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U25" t="n">
         <v>2.7778</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V25" t="n">
         <v>-0.05479999999999974</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W25" t="n">
         <v>2.8272</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X25" t="n">
         <v>-2.8819</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
